--- a/Bash Commands & Simulation Info.xlsx
+++ b/Bash Commands & Simulation Info.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harrisonwarke/Documents/FPGA Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA53D4D8-A971-B444-B70D-0C1D09C01282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA954E64-48AE-A747-B990-A472587554BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{B5ED1AD9-680E-6146-9023-A0DDD4422510}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{B5ED1AD9-680E-6146-9023-A0DDD4422510}"/>
   </bookViews>
   <sheets>
     <sheet name="Bash Commands" sheetId="1" r:id="rId1"/>
     <sheet name="verilog simulation" sheetId="3" r:id="rId2"/>
     <sheet name="compile verilog design command" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -112,9 +113,6 @@
     <t>----&gt;</t>
   </si>
   <si>
-    <t>external_LED.v</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -137,9 +135,6 @@
     </r>
   </si>
   <si>
-    <t>external_LED_tb.v</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -160,9 +155,6 @@
       </rPr>
       <t>(include the .vvp extension)</t>
     </r>
-  </si>
-  <si>
-    <t>test_project2.vvp</t>
   </si>
   <si>
     <t>enter the 3 fields below to create a command line argument for iVerilog</t>
@@ -217,6 +209,15 @@
       </rPr>
       <t>gtkwave &lt;nameofyoursimulationbinary&gt;.vcd</t>
     </r>
+  </si>
+  <si>
+    <t>combinational_logic.v</t>
+  </si>
+  <si>
+    <t>test_project4.vvp</t>
+  </si>
+  <si>
+    <t>combinational_logic_tb.v</t>
   </si>
 </sst>
 </file>
@@ -917,27 +918,27 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -952,7 +953,7 @@
   <cols>
     <col min="1" max="1" width="42.33203125" customWidth="1"/>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="4" max="4" width="58.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.2">
@@ -962,7 +963,7 @@
       <c r="B2" s="10"/>
       <c r="C2" s="9"/>
       <c r="D2" s="15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
@@ -976,29 +977,29 @@
         <v>17</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
@@ -1007,14 +1008,14 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D8" t="str">
         <f>"iverilog -o " &amp; D6 &amp; " " &amp; D4 &amp; " " &amp; D5</f>
-        <v>iverilog -o test_project2.vvp external_LED.v external_LED_tb.v</v>
+        <v>iverilog -o test_project4.vvp combinational_logic.v combinational_logic_tb.v</v>
       </c>
     </row>
   </sheetData>

--- a/Bash Commands & Simulation Info.xlsx
+++ b/Bash Commands & Simulation Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harrisonwarke/Documents/FPGA Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA954E64-48AE-A747-B990-A472587554BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFF7039-97E5-C54D-BA09-9862433E7619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{B5ED1AD9-680E-6146-9023-A0DDD4422510}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="2" xr2:uid="{B5ED1AD9-680E-6146-9023-A0DDD4422510}"/>
   </bookViews>
   <sheets>
     <sheet name="Bash Commands" sheetId="1" r:id="rId1"/>
@@ -211,13 +211,13 @@
     </r>
   </si>
   <si>
-    <t>combinational_logic.v</t>
-  </si>
-  <si>
-    <t>test_project4.vvp</t>
-  </si>
-  <si>
-    <t>combinational_logic_tb.v</t>
+    <t>two_to_one_multiplexer.v</t>
+  </si>
+  <si>
+    <t>two_to_one_multiplexer_tb.v</t>
+  </si>
+  <si>
+    <t>test_project5.vvp</t>
   </si>
 </sst>
 </file>
@@ -953,7 +953,7 @@
   <cols>
     <col min="1" max="1" width="42.33203125" customWidth="1"/>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="4" max="4" width="63.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.2">
@@ -988,7 +988,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
@@ -999,7 +999,7 @@
         <v>17</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D8" t="str">
         <f>"iverilog -o " &amp; D6 &amp; " " &amp; D4 &amp; " " &amp; D5</f>
-        <v>iverilog -o test_project4.vvp combinational_logic.v combinational_logic_tb.v</v>
+        <v>iverilog -o test_project5.vvp two_to_one_multiplexer.v two_to_one_multiplexer_tb.v</v>
       </c>
     </row>
   </sheetData>

--- a/Bash Commands & Simulation Info.xlsx
+++ b/Bash Commands & Simulation Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harrisonwarke/Documents/FPGA Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFF7039-97E5-C54D-BA09-9862433E7619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16864CEC-7FA3-A04B-8269-2FCADE3A6ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="2" xr2:uid="{B5ED1AD9-680E-6146-9023-A0DDD4422510}"/>
   </bookViews>
@@ -211,13 +211,13 @@
     </r>
   </si>
   <si>
-    <t>two_to_one_multiplexer.v</t>
-  </si>
-  <si>
-    <t>two_to_one_multiplexer_tb.v</t>
-  </si>
-  <si>
-    <t>test_project5.vvp</t>
+    <t>multiplexer_behavioural_tb.v</t>
+  </si>
+  <si>
+    <t>test_project6.vvp</t>
+  </si>
+  <si>
+    <t>multiplexer_behavioural.v</t>
   </si>
 </sst>
 </file>
@@ -977,7 +977,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
@@ -988,7 +988,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
@@ -999,7 +999,7 @@
         <v>17</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D8" t="str">
         <f>"iverilog -o " &amp; D6 &amp; " " &amp; D4 &amp; " " &amp; D5</f>
-        <v>iverilog -o test_project5.vvp two_to_one_multiplexer.v two_to_one_multiplexer_tb.v</v>
+        <v>iverilog -o test_project6.vvp multiplexer_behavioural.v multiplexer_behavioural_tb.v</v>
       </c>
     </row>
   </sheetData>
